--- a/target/test-classes/testdata/SignUpData.xlsx
+++ b/target/test-classes/testdata/SignUpData.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Local\DXC\iot-fe-automation\src\test\resources\testdata\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maria\Downloads\QA_Automation\s2-selenium\src\test\resources\testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18E91B0D-1D20-4580-854C-C75342578234}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4FC66C6-F58E-4A5D-85F5-E8445F8200F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3640" yWindow="3640" windowWidth="19200" windowHeight="9970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="22695" windowHeight="14476" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="signup" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="35">
   <si>
     <t>testCaseId</t>
   </si>
@@ -100,12 +100,6 @@
     <t>8 characters</t>
   </si>
   <si>
-    <t>C:\Local\DXC\iot-fe-automation\src\test\resources\testdata\avatars\valid.png</t>
-  </si>
-  <si>
-    <t>valid@test.com</t>
-  </si>
-  <si>
     <t>John</t>
   </si>
   <si>
@@ -122,6 +116,15 @@
   </si>
   <si>
     <t>dynamic email changes every runtime</t>
+  </si>
+  <si>
+    <t>src/test/resources/testdata/avatars/valid.png</t>
+  </si>
+  <si>
+    <t>Pass123#</t>
+  </si>
+  <si>
+    <t>duplicate@test.com</t>
   </si>
 </sst>
 </file>
@@ -531,7 +534,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J6"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
     <col min="2" max="2" width="36" customWidth="1"/>
@@ -544,7 +547,7 @@
     <col min="10" max="10" width="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -576,7 +579,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
         <v>10</v>
       </c>
@@ -584,29 +587,29 @@
         <v>11</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="F2" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>30</v>
-      </c>
       <c r="H2" s="4" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>12</v>
       </c>
       <c r="J2" s="2"/>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A3" s="3" t="s">
         <v>13</v>
       </c>
@@ -614,20 +617,20 @@
         <v>14</v>
       </c>
       <c r="C3" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="D3" s="3" t="s">
-        <v>28</v>
-      </c>
       <c r="E3" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F3" s="3"/>
       <c r="G3" s="5" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="I3" s="3" t="s">
         <v>15</v>
@@ -636,7 +639,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
         <v>17</v>
       </c>
@@ -656,7 +659,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A5" s="3" t="s">
         <v>19</v>
       </c>
@@ -664,22 +667,22 @@
         <v>20</v>
       </c>
       <c r="C5" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D5" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="D5" s="3" t="s">
-        <v>28</v>
-      </c>
       <c r="E5" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="I5" s="3" t="s">
         <v>21</v>
@@ -688,24 +691,24 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A6" s="2" t="s">
         <v>23</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>28</v>
-      </c>
       <c r="E6" s="2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>24</v>
@@ -728,9 +731,9 @@
     <hyperlink ref="G2" r:id="rId4" xr:uid="{498EB67A-803B-48D5-8D59-904424EC672D}"/>
     <hyperlink ref="H3" r:id="rId5" xr:uid="{2168F73D-A2F4-4F4D-B0B8-E07E3F9D6525}"/>
     <hyperlink ref="F5" r:id="rId6" xr:uid="{667CAB59-B8A7-4756-8957-95C7FC94E68C}"/>
-    <hyperlink ref="G5" r:id="rId7" xr:uid="{C2C0B56D-3C2D-4F0A-917C-786E863F6D00}"/>
+    <hyperlink ref="G5" r:id="rId7" display="Pass@123" xr:uid="{C2C0B56D-3C2D-4F0A-917C-786E863F6D00}"/>
     <hyperlink ref="F6" r:id="rId8" xr:uid="{79D05C1C-9924-4159-A8BD-09B438881738}"/>
-    <hyperlink ref="H5" r:id="rId9" xr:uid="{31D8F22C-F5EE-4145-8D0C-A7ACDC6E9A72}"/>
+    <hyperlink ref="H5" r:id="rId9" display="Pass@123" xr:uid="{31D8F22C-F5EE-4145-8D0C-A7ACDC6E9A72}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/target/test-classes/testdata/SignUpData.xlsx
+++ b/target/test-classes/testdata/SignUpData.xlsx
@@ -1,170 +1,55 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maria\Downloads\QA_Automation\s2-selenium\src\test\resources\testdata\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4FC66C6-F58E-4A5D-85F5-E8445F8200F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="22695" windowHeight="14476" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-98" yWindow="-98" windowWidth="22695" windowHeight="14476" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="signup" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="signup" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="35">
-  <si>
-    <t>testCaseId</t>
-  </si>
-  <si>
-    <t>scenario</t>
-  </si>
-  <si>
-    <t>avatarPath</t>
-  </si>
-  <si>
-    <t>firstName</t>
-  </si>
-  <si>
-    <t>lastName</t>
-  </si>
-  <si>
-    <t>email</t>
-  </si>
-  <si>
-    <t>password</t>
-  </si>
-  <si>
-    <t>confirmPassword</t>
-  </si>
-  <si>
-    <t>expectedOutcome</t>
-  </si>
-  <si>
-    <t>expectedErrorContains</t>
-  </si>
-  <si>
-    <t>TC-FE-A001</t>
-  </si>
-  <si>
-    <t>Valid sign-up</t>
-  </si>
-  <si>
-    <t>success</t>
-  </si>
-  <si>
-    <t>TC-FE-A002</t>
-  </si>
-  <si>
-    <t>Empty email</t>
-  </si>
-  <si>
-    <t>fieldError</t>
-  </si>
-  <si>
-    <t>required</t>
-  </si>
-  <si>
-    <t>TC-FE-A003</t>
-  </si>
-  <si>
-    <t>All fields empty</t>
-  </si>
-  <si>
-    <t>TC-FE-A004</t>
-  </si>
-  <si>
-    <t>Duplicate email</t>
-  </si>
-  <si>
-    <t>bannerError</t>
-  </si>
-  <si>
-    <t>already exists</t>
-  </si>
-  <si>
-    <t>TC-FE-A005</t>
-  </si>
-  <si>
-    <t>Ab@1234</t>
-  </si>
-  <si>
-    <t>8 characters</t>
-  </si>
-  <si>
-    <t>John</t>
-  </si>
-  <si>
-    <t>Doe</t>
-  </si>
-  <si>
-    <t>Pass@123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Password too short </t>
-  </si>
-  <si>
-    <t>ab@test.com</t>
-  </si>
-  <si>
-    <t>dynamic email changes every runtime</t>
-  </si>
-  <si>
-    <t>src/test/resources/testdata/avatars/valid.png</t>
-  </si>
-  <si>
-    <t>Pass123#</t>
-  </si>
-  <si>
-    <t>duplicate@test.com</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="4">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="10"/>
+      <sz val="11"/>
+      <u val="single"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -207,44 +92,103 @@
     </border>
   </borders>
   <cellStyleXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="7">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -532,208 +476,316 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:J6"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="13" customWidth="1"/>
-    <col min="2" max="2" width="36" customWidth="1"/>
-    <col min="3" max="3" width="50" customWidth="1"/>
-    <col min="4" max="4" width="12" customWidth="1"/>
-    <col min="5" max="5" width="11" customWidth="1"/>
-    <col min="6" max="6" width="33" customWidth="1"/>
-    <col min="7" max="7" width="12" customWidth="1"/>
-    <col min="8" max="9" width="18" customWidth="1"/>
-    <col min="10" max="10" width="24" customWidth="1"/>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="33" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="9"/>
+    <col width="24" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>testCaseId</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>scenario</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>avatarPath</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>firstName</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>lastName</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>password</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>confirmPassword</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>expectedOutcome</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>expectedErrorContains</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A2" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="F2" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="J2" s="2"/>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>TC-FE-A001</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Valid sign-up</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>src/test/resources/testdata/avatars/valid.png</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>John</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Doe</t>
+        </is>
+      </c>
+      <c r="F2" s="6" t="inlineStr">
+        <is>
+          <t>dynamic email changes every runtime</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>Pass@123</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>Pass@123</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="n"/>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A3" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F3" s="3"/>
-      <c r="G3" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="H3" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>16</v>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>TC-FE-A002</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Empty email</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>src/test/resources/testdata/avatars/valid.png</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>John</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Doe</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="n"/>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>Pass@123</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>Pass@123</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>fieldError</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A4" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>16</v>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>TC-FE-A003</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>All fields empty</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="n"/>
+      <c r="D4" s="2" t="n"/>
+      <c r="E4" s="2" t="n"/>
+      <c r="F4" s="2" t="n"/>
+      <c r="G4" s="2" t="n"/>
+      <c r="H4" s="2" t="n"/>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>fieldError</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A5" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="H5" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>22</v>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>TC-FE-A004</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Duplicate email</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>src/test/resources/testdata/avatars/valid.png</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>John</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Doe</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>valid@test.com</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>Pass123#</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>Pass123#</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>bannerError</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>already exists</t>
+        </is>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A6" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>25</v>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>TC-FE-A005</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Password too short </t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>src/test/resources/testdata/avatars/valid.png</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>John</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Doe</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>ab@test.com</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>Ab@1234</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>Ab@1234</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>fieldError</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>8 characters</t>
+        </is>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="F2" r:id="rId1" display="signup@test.com" xr:uid="{5ABA001B-3F4A-4A44-A9E2-43146BE3CCF6}"/>
-    <hyperlink ref="G3" r:id="rId2" xr:uid="{AE63EE9D-5B35-486F-AC69-C5061A0B8E02}"/>
-    <hyperlink ref="H2" r:id="rId3" xr:uid="{CFF8BD69-5B01-4759-A297-B5B8836C3E17}"/>
-    <hyperlink ref="G2" r:id="rId4" xr:uid="{498EB67A-803B-48D5-8D59-904424EC672D}"/>
-    <hyperlink ref="H3" r:id="rId5" xr:uid="{2168F73D-A2F4-4F4D-B0B8-E07E3F9D6525}"/>
-    <hyperlink ref="F5" r:id="rId6" xr:uid="{667CAB59-B8A7-4756-8957-95C7FC94E68C}"/>
-    <hyperlink ref="G5" r:id="rId7" display="Pass@123" xr:uid="{C2C0B56D-3C2D-4F0A-917C-786E863F6D00}"/>
-    <hyperlink ref="F6" r:id="rId8" xr:uid="{79D05C1C-9924-4159-A8BD-09B438881738}"/>
-    <hyperlink ref="H5" r:id="rId9" display="Pass@123" xr:uid="{31D8F22C-F5EE-4145-8D0C-A7ACDC6E9A72}"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2" display="signup@test.com" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H2" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H3" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F5" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G5" display="Pass@123" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H5" display="Pass@123" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F6" r:id="rId9"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
